--- a/assets/infobasica/planilhas/aula16_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula16_nivel2.xlsx
@@ -1550,7 +1550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Taxa numa célula fixa: =B2(1+$E$1); na coluna C, =SE(B3&gt;=2$B$2; "Dobrou"; "") marca os meses em que o valor já dobrou.</t>
+          <t>Taxa numa célula fixa: =B2*(1+$E$1); na coluna C, =SE(B3&gt;=2*$B$2; "Dobrou"; "") marca os meses em que o valor já dobrou.</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
